--- a/data/产品数据.xlsx
+++ b/data/产品数据.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A-myprofile\zudao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\a_myprofile\zudao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E94FC6-B956-497A-91F9-E70D97B18837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DADCBA6-01A4-4114-9024-C6043CE8CEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6150" yWindow="1250" windowWidth="19200" windowHeight="9970" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4176" yWindow="1272" windowWidth="11844" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,37 +30,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
-  <si>
-    <t>宽度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>种类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="13">
   <si>
     <t>种类</t>
   </si>
@@ -73,32 +55,61 @@
   <si>
     <t>重量</t>
   </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>面积利用率：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>样例三</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>样例二</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>样例一</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段切解码</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最佳适配解码</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>simple解码</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -107,16 +118,50 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -126,23 +171,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -155,9 +242,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,15 +276,15 @@
         <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -267,132 +354,167 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -404,173 +526,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>130</v>
-      </c>
-      <c r="B3">
-        <v>445</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-      <c r="D3">
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>492</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1023</v>
+      </c>
+      <c r="C3" s="2">
+        <v>455</v>
+      </c>
+      <c r="D3" s="7">
         <v>544.947</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <f>D3/(A3*B3*C3)</f>
-        <v>9.4199999999999996E-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>500</v>
-      </c>
-      <c r="B4">
-        <v>833</v>
-      </c>
-      <c r="C4">
-        <v>1000</v>
-      </c>
-      <c r="D4">
+        <v>2.3795899877725214E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>266</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1080</v>
+      </c>
+      <c r="C4" s="2">
+        <v>341</v>
+      </c>
+      <c r="D4" s="7">
         <v>3923.43</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>547</v>
-      </c>
-      <c r="B5">
-        <v>291</v>
-      </c>
-      <c r="C5">
-        <v>500</v>
-      </c>
-      <c r="D5">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>220</v>
+      </c>
+      <c r="B5" s="2">
+        <v>175</v>
+      </c>
+      <c r="C5" s="2">
+        <v>15000</v>
+      </c>
+      <c r="D5" s="7">
         <f>A5*B5*C5*F3</f>
-        <v>749.72366999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1374.213217938631</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>240</v>
+      </c>
+      <c r="B6" s="8">
+        <v>285</v>
+      </c>
+      <c r="C6" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>130</v>
-      </c>
-      <c r="B3">
-        <v>445</v>
-      </c>
-      <c r="C3">
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>436</v>
+      </c>
+      <c r="B3" s="2">
+        <v>722</v>
+      </c>
+      <c r="C3" s="2">
         <v>1000</v>
       </c>
-      <c r="D3">
-        <v>544.947</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>500</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>833</v>
       </c>
-      <c r="C4">
-        <v>1000</v>
-      </c>
-      <c r="D4">
-        <v>3923.43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="C4" s="2">
+        <v>555</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>547</v>
       </c>
-      <c r="B5">
-        <v>291</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
+        <v>631</v>
+      </c>
+      <c r="C5" s="2">
+        <v>400</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>211</v>
+      </c>
+      <c r="B6" s="8">
+        <v>342</v>
+      </c>
+      <c r="C6" s="8">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>420</v>
+      </c>
+      <c r="B7" s="8">
+        <v>832</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -579,221 +741,235 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
         <v>4</v>
       </c>
-      <c r="B1">
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>130</v>
-      </c>
-      <c r="B3">
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>230</v>
+      </c>
+      <c r="B3" s="2">
         <v>445</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>1000</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="7">
         <v>544.947</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <f>D3/(A3*B3*C3)</f>
-        <v>9.4199999999999996E-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+        <v>5.3243478260869569E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>500</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>833</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1000</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>3923.43</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>547</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>291</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>500</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <f>A5*B5*C5*F3</f>
-        <v>749.72366999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+        <v>423.75685695652174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>200</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>555</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>666</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <f>A6*B6*C6*$F$3</f>
-        <v>696.38292000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>393.6077373913044</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7548A172-3187-4931-B606-EA18563F2873}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>230</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>445</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>1000</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="7">
         <v>544.947</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <f>D3/(A3*B3*C3)</f>
         <v>5.3243478260869569E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>500</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>833</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1000</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>3923.43</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>547</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>291</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>500</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <f>A5*B5*C5*F3</f>
         <v>423.75685695652174</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>200</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>555</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>666</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <f>A6*B6*C6*$F$3</f>
         <v>393.6077373913044</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>400</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>600</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>888</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <f>A7*B7*C7*$F$3</f>
         <v>1134.7250086956521</v>
       </c>
@@ -802,4 +978,601 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28853C7-4396-4138-8E11-BE4327529CB9}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>450</v>
+      </c>
+      <c r="B3" s="2">
+        <v>690</v>
+      </c>
+      <c r="C3" s="2">
+        <v>29</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>280</v>
+      </c>
+      <c r="B4" s="2">
+        <v>833</v>
+      </c>
+      <c r="C4" s="2">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>250</v>
+      </c>
+      <c r="B5" s="2">
+        <v>470</v>
+      </c>
+      <c r="C5" s="2">
+        <v>23</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>300</v>
+      </c>
+      <c r="B6" s="2">
+        <v>275</v>
+      </c>
+      <c r="C6" s="2">
+        <v>9</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>380</v>
+      </c>
+      <c r="B7" s="2">
+        <v>720</v>
+      </c>
+      <c r="C7" s="2">
+        <v>38</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C5524DF-3114-4322-A8DB-30B6DB9FF217}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>500</v>
+      </c>
+      <c r="B3" s="2">
+        <v>900</v>
+      </c>
+      <c r="C3" s="2">
+        <v>102</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>500</v>
+      </c>
+      <c r="B4" s="2">
+        <v>450</v>
+      </c>
+      <c r="C4" s="2">
+        <v>123</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>250</v>
+      </c>
+      <c r="B5" s="2">
+        <v>900</v>
+      </c>
+      <c r="C5" s="2">
+        <v>210</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>250</v>
+      </c>
+      <c r="B6" s="2">
+        <v>450</v>
+      </c>
+      <c r="C6" s="2">
+        <v>186</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>200</v>
+      </c>
+      <c r="B7" s="2">
+        <v>600</v>
+      </c>
+      <c r="C7" s="2">
+        <v>138</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E47CB2AD-0E88-4FD3-BD78-4B7DCB0770F0}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A1" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14">
+        <v>5</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="14">
+        <v>5</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14">
+        <v>5</v>
+      </c>
+      <c r="K2" s="15"/>
+    </row>
+    <row r="3" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A4" s="14">
+        <v>230</v>
+      </c>
+      <c r="B4" s="14">
+        <v>445</v>
+      </c>
+      <c r="C4" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="14">
+        <v>500</v>
+      </c>
+      <c r="F4" s="14">
+        <v>900</v>
+      </c>
+      <c r="G4" s="14">
+        <v>102</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="14">
+        <v>450</v>
+      </c>
+      <c r="J4" s="14">
+        <v>690</v>
+      </c>
+      <c r="K4" s="14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A5" s="14">
+        <v>500</v>
+      </c>
+      <c r="B5" s="14">
+        <v>833</v>
+      </c>
+      <c r="C5" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="14">
+        <v>500</v>
+      </c>
+      <c r="F5" s="14">
+        <v>450</v>
+      </c>
+      <c r="G5" s="14">
+        <v>123</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="14">
+        <v>280</v>
+      </c>
+      <c r="J5" s="14">
+        <v>833</v>
+      </c>
+      <c r="K5" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A6" s="14">
+        <v>547</v>
+      </c>
+      <c r="B6" s="14">
+        <v>291</v>
+      </c>
+      <c r="C6" s="14">
+        <v>500</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="14">
+        <v>250</v>
+      </c>
+      <c r="F6" s="14">
+        <v>900</v>
+      </c>
+      <c r="G6" s="14">
+        <v>210</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="14">
+        <v>250</v>
+      </c>
+      <c r="J6" s="14">
+        <v>470</v>
+      </c>
+      <c r="K6" s="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A7" s="14">
+        <v>200</v>
+      </c>
+      <c r="B7" s="14">
+        <v>555</v>
+      </c>
+      <c r="C7" s="14">
+        <v>666</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="14">
+        <v>250</v>
+      </c>
+      <c r="F7" s="14">
+        <v>450</v>
+      </c>
+      <c r="G7" s="14">
+        <v>186</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="14">
+        <v>300</v>
+      </c>
+      <c r="J7" s="14">
+        <v>275</v>
+      </c>
+      <c r="K7" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A8" s="14">
+        <v>400</v>
+      </c>
+      <c r="B8" s="14">
+        <v>600</v>
+      </c>
+      <c r="C8" s="14">
+        <v>888</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="14">
+        <v>200</v>
+      </c>
+      <c r="F8" s="14">
+        <v>600</v>
+      </c>
+      <c r="G8" s="14">
+        <v>138</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="14">
+        <v>380</v>
+      </c>
+      <c r="J8" s="14">
+        <v>720</v>
+      </c>
+      <c r="K8" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+    </row>
+    <row r="10" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A10" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A11" s="17">
+        <v>0.9637</v>
+      </c>
+      <c r="B11" s="18">
+        <v>0.91869999999999996</v>
+      </c>
+      <c r="C11" s="18">
+        <v>0.86670000000000003</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="18">
+        <v>0.98060000000000003</v>
+      </c>
+      <c r="F11" s="17">
+        <v>0.99009999999999998</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="18">
+        <v>0.9234</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0.95050000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="24.6" x14ac:dyDescent="0.5">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="18" spans="4:4" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="D18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E9:G9"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>